--- a/examples/收件人清单示例（演示数据）.xlsx
+++ b/examples/收件人清单示例（演示数据）.xlsx
@@ -603,7 +603,11 @@
           <t>北京中关军融创启信息技术有限公司</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>演示专用水印</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>zg@rongchuang-demo.cn</t>
@@ -612,11 +616,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>演示专用水印</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
     </row>

--- a/examples/收件人清单示例（演示数据）.xlsx
+++ b/examples/收件人清单示例（演示数据）.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -463,12 +467,17 @@
           <t>附件路径</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>合并组</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
         <is>
           <t>打开口令</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>权限口令</t>
         </is>
@@ -480,7 +489,6 @@
           <t>苏州启衡科技有限公司</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>ir@qiheng-demo.cn</t>
@@ -491,11 +499,7 @@
           <t>fin@qiheng-demo.cn</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -503,22 +507,17 @@
           <t>宁波晨曦汐诺供应链股份有限公司</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>contact@chenxi-demo.cn</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
         <is>
           <t>Demo-Open-88</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -526,7 +525,6 @@
           <t>新疆乌鲁木齐市泓远红杉智能科技有限公司</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>admin@hongyuan-demo.cn</t>
@@ -542,10 +540,7 @@
           <t>audit@hongyuan-demo.cn</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -553,22 +548,17 @@
           <t>上海临港科创一期产业投资有限公司</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>lg@chuangxin-demo.cn</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>临港科创2026年度交付文件</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -576,7 +566,6 @@
           <t>珠海横琴粤澳深谋咨询服务有限公司</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>gp@henqin-demo.cn</t>
@@ -587,11 +576,8 @@
           <t>fin@henqin-demo.cn</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Demo-Owner-66</t>
         </is>
@@ -613,12 +599,7 @@
           <t>zg@rongchuang-demo.cn</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -626,18 +607,12 @@
           <t>深圳前海深港现代服务业合作区汇金聚富实业有限公司</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>huijin@qianhai-demo.cn</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -645,7 +620,6 @@
           <t>杭州西湖区云栖数字经济研究院</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>yunqi@xihu-demo.cn</t>
@@ -656,11 +630,7 @@
           <t>ir@xihu-demo.cn</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/examples/收件人清单示例（演示数据）.xlsx
+++ b/examples/收件人清单示例（演示数据）.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -462,22 +462,17 @@
           <t>邮件标题</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>附件路径</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>合并组</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>打开口令</t>
+        </is>
+      </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>打开口令</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>权限口令</t>
         </is>
@@ -499,7 +494,6 @@
           <t>fin@qiheng-demo.cn</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,8 +506,7 @@
           <t>contact@chenxi-demo.cn</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Demo-Open-88</t>
         </is>
@@ -540,7 +533,6 @@
           <t>audit@hongyuan-demo.cn</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -558,7 +550,6 @@
           <t>临港科创2026年度交付文件</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -576,8 +567,7 @@
           <t>fin@henqin-demo.cn</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Demo-Owner-66</t>
         </is>
@@ -599,7 +589,6 @@
           <t>zg@rongchuang-demo.cn</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -612,7 +601,6 @@
           <t>huijin@qianhai-demo.cn</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -630,7 +618,6 @@
           <t>ir@xihu-demo.cn</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
